--- a/tools/importer/reports/import-ypi-v1.report.xlsx
+++ b/tools/importer/reports/import-ypi-v1.report.xlsx
@@ -213,13 +213,13 @@
     <t>en/home/get-involved/young-professional-initiative.report.json</t>
   </si>
   <si>
-    <t>["hero-text-up","center-intro(future-of-giving)","columns(what-is-ypi,image-right)","spacer(yellow-strip)","columns(impact,image-left,yellow)","quote-image(labanowski)","spacer(yellow-strip)","columns(ways,image-left,yellow)","spacer(trailing-black-band)"]</t>
+    <t>["hero-text-up-tall","center-intro(future-of-giving)","columns(what-is-ypi,image-right)","spacer(yellow-strip)","columns(impact,image-left,yellow)","quote-image(labanowski)","spacer(yellow-strip)","columns(ways,image-left,yellow)","spacer(trailing-black-band)"]</t>
   </si>
   <si>
     <t>en/home/get-involved/young-professional-initiative</t>
   </si>
   <si>
-    <t>2026-09-08T22:25:12.883Z</t>
+    <t>2026-09-08T22:47:49.236Z</t>
   </si>
   <si>
     <t>Young Professional Initiative</t>
